--- a/Checklist - Artefato 2.xlsx
+++ b/Checklist - Artefato 2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pucpredu-my.sharepoint.com/personal/ferrarini_isabela_pucpr_edu_br/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael Fernandes\Downloads\ChecklistQualidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2335335-E77E-46DA-B191-DBDC4ACA7201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC326C9-D6D8-4D3F-93F2-C82861A2BD7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>N°</t>
   </si>
@@ -137,13 +137,28 @@
   </si>
   <si>
     <t>Tempo total:</t>
+  </si>
+  <si>
+    <t>Aderência Por Área</t>
+  </si>
+  <si>
+    <t>Total de Perguntas</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>Não Aplicavél</t>
+  </si>
+  <si>
+    <t>Aderência</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -184,8 +199,30 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -196,6 +233,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFA6124E"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA6124E"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -278,7 +321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -293,10 +336,26 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -577,7 +636,7 @@
     <col min="6" max="6" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" ht="46.8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -621,7 +680,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -635,7 +694,7 @@
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -649,7 +708,7 @@
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -663,7 +722,7 @@
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -677,7 +736,7 @@
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -691,7 +750,7 @@
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -705,7 +764,7 @@
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -719,7 +778,7 @@
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -733,7 +792,7 @@
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -747,7 +806,7 @@
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -761,7 +820,7 @@
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -775,7 +834,7 @@
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -789,7 +848,7 @@
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -803,7 +862,7 @@
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -817,7 +876,7 @@
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -831,7 +890,7 @@
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -845,7 +904,7 @@
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -859,7 +918,7 @@
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -873,7 +932,7 @@
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -887,7 +946,7 @@
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -902,10 +961,16 @@
       <c r="H21" s="5"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="9"/>
+      <c r="C25" s="8"/>
+      <c r="E25" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="6" t="s">
@@ -914,6 +979,18 @@
       <c r="C26" s="7" t="s">
         <v>30</v>
       </c>
+      <c r="E26" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="6" t="s">
@@ -922,6 +999,10 @@
       <c r="C27" s="7" t="s">
         <v>32</v>
       </c>
+      <c r="E27" s="12"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="13"/>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="6" t="s">
@@ -930,6 +1011,18 @@
       <c r="C28" s="7" t="s">
         <v>34</v>
       </c>
+      <c r="E28" s="14">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14">
+        <v>0</v>
+      </c>
+      <c r="G28" s="14">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="6"/>
@@ -956,6 +1049,13 @@
       <c r="C32" s="7"/>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="H26:H27"/>
+  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -964,6 +1064,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007CCF20922A0DE34DA3357EDA40AE3850" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df2c289d3a08b18055ba2ef47a57998b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="aed73f09-bf5d-4147-a3d9-eca4840d3416" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="91dac5f1c2bd6141b57005fd2a16424c" ns3:_="">
     <xsd:import namespace="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
@@ -1113,15 +1222,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1131,6 +1231,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{398CE32A-8B97-402C-8C2F-6E1932019FB4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F3887D1-A29C-405D-BB37-6D7E8E326CC9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1144,14 +1252,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{398CE32A-8B97-402C-8C2F-6E1932019FB4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Checklist - Artefato 2.xlsx
+++ b/Checklist - Artefato 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael Fernandes\Downloads\ChecklistQualidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC326C9-D6D8-4D3F-93F2-C82861A2BD7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8D7DDD-EC4D-4103-BE89-B853C42A8EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -337,24 +337,24 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -961,16 +961,16 @@
       <c r="H21" s="5"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C25" s="8"/>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="6" t="s">
@@ -979,16 +979,16 @@
       <c r="C26" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="G26" s="10" t="s">
+      <c r="G26" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H26" s="11" t="s">
+      <c r="H26" s="14" t="s">
         <v>43</v>
       </c>
     </row>
@@ -999,10 +999,10 @@
       <c r="C27" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E27" s="12"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="15"/>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="6" t="s">
@@ -1011,16 +1011,16 @@
       <c r="C28" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="9">
         <v>0</v>
       </c>
-      <c r="F28" s="14">
+      <c r="F28" s="9">
         <v>0</v>
       </c>
-      <c r="G28" s="14">
+      <c r="G28" s="9">
         <v>0</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H28" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1073,6 +1073,14 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="aed73f09-bf5d-4147-a3d9-eca4840d3416" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007CCF20922A0DE34DA3357EDA40AE3850" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df2c289d3a08b18055ba2ef47a57998b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="aed73f09-bf5d-4147-a3d9-eca4840d3416" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="91dac5f1c2bd6141b57005fd2a16424c" ns3:_="">
     <xsd:import namespace="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
@@ -1222,14 +1230,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="aed73f09-bf5d-4147-a3d9-eca4840d3416" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{398CE32A-8B97-402C-8C2F-6E1932019FB4}">
   <ds:schemaRefs>
@@ -1239,6 +1239,22 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F272DB39-8BAE-464A-AAA3-19537EA33ACE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F3887D1-A29C-405D-BB37-6D7E8E326CC9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1254,20 +1270,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F272DB39-8BAE-464A-AAA3-19537EA33ACE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Checklist - Artefato 2.xlsx
+++ b/Checklist - Artefato 2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael Fernandes\Downloads\ChecklistQualidade\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Isabela\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8D7DDD-EC4D-4103-BE89-B853C42A8EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{361BD572-2FE5-4A37-AB67-0DB7DC23867E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="59">
   <si>
     <t>N°</t>
   </si>
@@ -152,6 +152,51 @@
   </si>
   <si>
     <t>Aderência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não conforme </t>
+  </si>
+  <si>
+    <t>O Artefato 2 apresenta o que o sistema faz, mas não descreve respostas do sistema às ações do usuário de forma suficiente para avaliar esse aspecto.</t>
+  </si>
+  <si>
+    <t>Médio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Em andamento </t>
+  </si>
+  <si>
+    <t>O Artefato 2 não apresenta ações corretivas ou tratamento de não conformidades.</t>
+  </si>
+  <si>
+    <t>O campo “Não é” afirma expressamente que o sistema não é emergencial.</t>
+  </si>
+  <si>
+    <t>O campo “Não faz” afirma explicitamente que o sistema não chama ambulâncias.</t>
+  </si>
+  <si>
+    <t>Conforme</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Atualizar o Artefato 2 detalhando o comportamento e o feedback da interface para cada ação do usuário</t>
+  </si>
+  <si>
+    <t>incluir uma seção dedicada no Artefato 2 para detalhar os procedimentos de identificação, registro e plano de tratamento das não conformidades</t>
+  </si>
+  <si>
+    <t>Revisar o texto descritivo do sistema, garantindo que o escopo e o propósito não emergencial fiquem claros e coerentes em todos os campos</t>
+  </si>
+  <si>
+    <t>Ajustar a documentação do projeto para esclarecer expressamente o limite de atuação do sistema, indicando alternativas ou contatos para casos de emergência real.</t>
+  </si>
+  <si>
+    <t>Corrigir os termos da documentação para especificar claramente que a plataforma atua apenas na intermediação/agendamento, e não na contratação direta de profissionais de saúde</t>
+  </si>
+  <si>
+    <t>Matheus</t>
   </si>
 </sst>
 </file>
@@ -321,7 +366,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -341,6 +386,25 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -629,14 +693,16 @@
   <dimension ref="A1:Z32"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="107.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="116" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" customWidth="1"/>
-    <col min="5" max="5" width="15.109375" customWidth="1"/>
+    <col min="4" max="4" width="21.5546875" customWidth="1"/>
+    <col min="5" max="5" width="37.21875" customWidth="1"/>
     <col min="6" max="6" width="14.21875" customWidth="1"/>
+    <col min="7" max="7" width="40.33203125" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="46.8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -687,12 +753,24 @@
       <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
+      <c r="C2" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="3" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
@@ -701,12 +779,24 @@
       <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
+      <c r="C3" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="4" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
@@ -715,12 +805,24 @@
       <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
+      <c r="C4" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="5" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
@@ -729,12 +831,24 @@
       <c r="B5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
+      <c r="C5" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="6" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
@@ -743,12 +857,24 @@
       <c r="B6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
+      <c r="C6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="7" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
@@ -757,12 +883,24 @@
       <c r="B7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
+      <c r="C7" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="8" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
@@ -771,12 +909,24 @@
       <c r="B8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+      <c r="C8" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="9" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
@@ -785,12 +935,24 @@
       <c r="B9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
+      <c r="C9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="10" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
@@ -799,12 +961,24 @@
       <c r="B10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
+      <c r="C10" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="11" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
@@ -813,40 +987,76 @@
       <c r="B11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+      <c r="C11" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A12" s="13">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-    </row>
-    <row r="13" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+      <c r="C12" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A13" s="13">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
+      <c r="C13" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="14" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
@@ -855,12 +1065,24 @@
       <c r="B14" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
+      <c r="C14" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="15" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
@@ -869,12 +1091,24 @@
       <c r="B15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
+      <c r="C15" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="16" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
@@ -883,68 +1117,128 @@
       <c r="B16" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-    </row>
-    <row r="17" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
+      <c r="C16" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" s="16" customFormat="1" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-    </row>
-    <row r="18" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
+      <c r="C17" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" s="16" customFormat="1" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="13">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-    </row>
-    <row r="19" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
+      <c r="C18" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" s="16" customFormat="1" ht="79.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="13">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-    </row>
-    <row r="20" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C19" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
+      <c r="C20" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="21" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
@@ -953,24 +1247,36 @@
       <c r="B21" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
+      <c r="C21" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C25" s="8"/>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="6" t="s">
@@ -979,16 +1285,16 @@
       <c r="C26" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="G26" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="H26" s="14" t="s">
+      <c r="H26" s="21" t="s">
         <v>43</v>
       </c>
     </row>
@@ -999,10 +1305,10 @@
       <c r="C27" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E27" s="13"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="15"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="22"/>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="6" t="s">
@@ -1012,16 +1318,16 @@
         <v>34</v>
       </c>
       <c r="E28" s="9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F28" s="9">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G28" s="9">
         <v>0</v>
       </c>
-      <c r="H28" s="9">
-        <v>0</v>
+      <c r="H28" s="17">
+        <v>0.75</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1057,8 +1363,9 @@
     <mergeCell ref="H26:H27"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1073,14 +1380,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="aed73f09-bf5d-4147-a3d9-eca4840d3416" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007CCF20922A0DE34DA3357EDA40AE3850" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df2c289d3a08b18055ba2ef47a57998b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="aed73f09-bf5d-4147-a3d9-eca4840d3416" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="91dac5f1c2bd6141b57005fd2a16424c" ns3:_="">
     <xsd:import namespace="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
@@ -1230,6 +1529,14 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="aed73f09-bf5d-4147-a3d9-eca4840d3416" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{398CE32A-8B97-402C-8C2F-6E1932019FB4}">
   <ds:schemaRefs>
@@ -1239,22 +1546,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F272DB39-8BAE-464A-AAA3-19537EA33ACE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F3887D1-A29C-405D-BB37-6D7E8E326CC9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1270,4 +1561,20 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F272DB39-8BAE-464A-AAA3-19537EA33ACE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>